--- a/data/trans_orig/IP24-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2007 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2007 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28985</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47983</t>
+          <t>48553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62587</t>
+          <t>62886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38495</t>
+          <t>38024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53828</t>
+          <t>52748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90868</t>
+          <t>89071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111662</t>
+          <t>110433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31125</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>49502</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>21457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49968</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43062</t>
+          <t>42827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65920</t>
+          <t>65225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41179</t>
+          <t>41481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>63631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87423</t>
+          <t>86402</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116489</t>
+          <t>116536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135039</t>
+          <t>135430</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>171745</t>
+          <t>171056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>213404</t>
+          <t>213153</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247581</t>
+          <t>247227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196761</t>
+          <t>196222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>230587</t>
+          <t>229519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>420484</t>
+          <t>422309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467665</t>
+          <t>468891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94756</t>
+          <t>94289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124461</t>
+          <t>123397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93660</t>
+          <t>94300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121935</t>
+          <t>122350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195822</t>
+          <t>195113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>236276</t>
+          <t>236447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34764</t>
+          <t>33398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42147</t>
+          <t>41883</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50466</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72269</t>
+          <t>73835</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77015</t>
+          <t>76943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98338</t>
+          <t>98967</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54379</t>
+          <t>54698</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74518</t>
+          <t>73647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137281</t>
+          <t>138138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>52508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>72573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97354</t>
+          <t>97671</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27331</t>
+          <t>27439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>44862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>55454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>79956</t>
+          <t>79595</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>107407</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79200</t>
+          <t>79811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106613</t>
+          <t>107468</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>127075</t>
+          <t>127004</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>160477</t>
+          <t>159591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>214184</t>
+          <t>212442</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>258943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>352060</t>
+          <t>353449</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>394220</t>
+          <t>394466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>301840</t>
+          <t>303217</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>341987</t>
+          <t>344012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>664717</t>
+          <t>667168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>726298</t>
+          <t>726522</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151082</t>
+          <t>149294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186581</t>
+          <t>186591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316124</t>
+          <t>313624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366254</t>
+          <t>366695</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2012 (tasa de respuesta: 98,95%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>21085</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23207</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37525</t>
+          <t>37865</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54664</t>
+          <t>54793</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48524</t>
+          <t>48466</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64021</t>
+          <t>63447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28272</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>42950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80358</t>
+          <t>80839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102658</t>
+          <t>103498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,21%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64826</t>
+          <t>64866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>50147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77400</t>
+          <t>76654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68420</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95587</t>
+          <t>95333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101527</t>
+          <t>100406</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133384</t>
+          <t>134200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179599</t>
+          <t>177868</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>221492</t>
+          <t>221229</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>235325</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268831</t>
+          <t>269474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215981</t>
+          <t>216691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252926</t>
+          <t>254283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>463111</t>
+          <t>462708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>513779</t>
+          <t>513424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84538</t>
+          <t>82659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112531</t>
+          <t>111240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65938</t>
+          <t>66771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94703</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159176</t>
+          <t>157831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198201</t>
+          <t>197125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28770</t>
+          <t>29028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46161</t>
+          <t>45548</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40118</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>59285</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74183</t>
+          <t>73635</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98753</t>
+          <t>99576</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80633</t>
+          <t>80168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102611</t>
+          <t>101100</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>64811</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86111</t>
+          <t>86619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149228</t>
+          <t>150190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181124</t>
+          <t>181674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>48713</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72426</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61688</t>
+          <t>61845</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88250</t>
+          <t>90619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81525</t>
+          <t>80221</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>113403</t>
+          <t>110805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115263</t>
+          <t>114813</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149438</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>177135</t>
+          <t>177595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>215654</t>
+          <t>217710</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>303362</t>
+          <t>300112</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>354816</t>
+          <t>351547</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>378825</t>
+          <t>375876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>423534</t>
+          <t>420823</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>325480</t>
+          <t>324882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369371</t>
+          <t>370798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>713588</t>
+          <t>711984</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>773977</t>
+          <t>775556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103709</t>
+          <t>102240</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136198</t>
+          <t>135423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>237962</t>
+          <t>238331</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285573</t>
+          <t>288270</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2016 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40857</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50771</t>
+          <t>51162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70098</t>
+          <t>69532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89376</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28564</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>34077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54784</t>
+          <t>54728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49652</t>
+          <t>50420</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75036</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66084</t>
+          <t>64498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93470</t>
+          <t>92242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99954</t>
+          <t>97863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131512</t>
+          <t>130902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>173087</t>
+          <t>173538</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>213755</t>
+          <t>213157</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251763</t>
+          <t>252530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>287014</t>
+          <t>286984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227389</t>
+          <t>229011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>265263</t>
+          <t>267596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495315</t>
+          <t>490591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>543891</t>
+          <t>539905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>89564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117850</t>
+          <t>117629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83500</t>
+          <t>87051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153776</t>
+          <t>155657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192355</t>
+          <t>193825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>37422</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33020</t>
+          <t>32921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52951</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58659</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84326</t>
+          <t>83940</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>82559</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>102838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72763</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94905</t>
+          <t>95472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161893</t>
+          <t>161129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>192606</t>
+          <t>193050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>48152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>55035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71684</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98908</t>
+          <t>97788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>24146</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75724</t>
+          <t>76538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79640</t>
+          <t>81353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110033</t>
+          <t>111763</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97764</t>
+          <t>98669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129761</t>
+          <t>129155</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>148413</t>
+          <t>147861</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>186263</t>
+          <t>186513</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>254627</t>
+          <t>255328</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>304513</t>
+          <t>305149</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>377563</t>
+          <t>377931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>418649</t>
+          <t>419266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351445</t>
+          <t>356063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>398442</t>
+          <t>400403</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>747219</t>
+          <t>741922</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>809419</t>
+          <t>803888</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>139898</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40449</t>
+          <t>41020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>71314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21582</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46197</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24309</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46839</t>
+          <t>46006</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43789</t>
+          <t>45015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70806</t>
+          <t>71541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73289</t>
+          <t>73775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109289</t>
+          <t>110101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62456</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94667</t>
+          <t>94773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111569</t>
+          <t>109368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151572</t>
+          <t>152368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179655</t>
+          <t>181754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237309</t>
+          <t>236416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>182112</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242183</t>
+          <t>244163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204055</t>
+          <t>200730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251060</t>
+          <t>250668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>399574</t>
+          <t>404786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>479101</t>
+          <t>482251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86265</t>
+          <t>85871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176241</t>
+          <t>176869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75042</t>
+          <t>75371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121635</t>
+          <t>124536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170887</t>
+          <t>169247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288500</t>
+          <t>271527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>46349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67060</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49531</t>
+          <t>48357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37051</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>73585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103427</t>
+          <t>103055</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52729</t>
+          <t>53486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>73335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>54681</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78038</t>
+          <t>78808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114775</t>
+          <t>114379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144631</t>
+          <t>145099</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>39336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>44611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67393</t>
+          <t>67025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36982</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43974</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69556</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79863</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>114773</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>131974</t>
+          <t>130717</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>175595</t>
+          <t>173814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104257</t>
+          <t>105792</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143290</t>
+          <t>145147</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160068</t>
+          <t>164197</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>208894</t>
+          <t>211456</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278987</t>
+          <t>275879</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>340051</t>
+          <t>340590</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>266342</t>
+          <t>270023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>337554</t>
+          <t>338815</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300735</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>354319</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>591215</t>
+          <t>588080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>677192</t>
+          <t>676870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125294</t>
+          <t>123419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>237599</t>
+          <t>227771</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>115769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>252212</t>
+          <t>254374</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>367025</t>
+          <t>366625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
